--- a/nasdaq_presidential_analysis.xlsx
+++ b/nasdaq_presidential_analysis.xlsx
@@ -506,28 +506,28 @@
         <v>31067</v>
       </c>
       <c r="E2" t="n">
-        <v>52.88</v>
+        <v>64.05</v>
       </c>
       <c r="F2" t="n">
-        <v>17.88</v>
+        <v>14.29</v>
       </c>
       <c r="G2" t="n">
-        <v>-33.12</v>
+        <v>-38.83</v>
       </c>
       <c r="H2" t="n">
-        <v>0.667</v>
+        <v>0.915</v>
       </c>
       <c r="I2" t="n">
-        <v>32.7</v>
+        <v>40.27</v>
       </c>
       <c r="J2" t="n">
-        <v>15.14</v>
+        <v>12.78</v>
       </c>
       <c r="K2" t="n">
-        <v>-19.42</v>
+        <v>-4.19</v>
       </c>
       <c r="L2" t="n">
-        <v>21.77</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="3">
@@ -550,28 +550,28 @@
         <v>32528</v>
       </c>
       <c r="E3" t="n">
-        <v>76</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>17.71</v>
+        <v>14.14</v>
       </c>
       <c r="G3" t="n">
-        <v>-28.95</v>
+        <v>-36.32</v>
       </c>
       <c r="H3" t="n">
-        <v>0.847</v>
+        <v>0.956</v>
       </c>
       <c r="I3" t="n">
-        <v>18.81</v>
+        <v>6.81</v>
       </c>
       <c r="J3" t="n">
-        <v>-10.35</v>
+        <v>-4.89</v>
       </c>
       <c r="K3" t="n">
-        <v>39.45</v>
+        <v>46.35</v>
       </c>
       <c r="L3" t="n">
-        <v>19.46</v>
+        <v>15.12</v>
       </c>
     </row>
     <row r="4">
@@ -594,28 +594,28 @@
         <v>33989</v>
       </c>
       <c r="E4" t="n">
-        <v>93.40000000000001</v>
+        <v>124.87</v>
       </c>
       <c r="F4" t="n">
-        <v>17.28</v>
+        <v>13.79</v>
       </c>
       <c r="G4" t="n">
-        <v>-10.07</v>
+        <v>-13.26</v>
       </c>
       <c r="H4" t="n">
-        <v>1.016</v>
+        <v>1.49</v>
       </c>
       <c r="I4" t="n">
-        <v>15.06</v>
+        <v>14.12</v>
       </c>
       <c r="J4" t="n">
-        <v>4.78</v>
+        <v>-4.74</v>
       </c>
       <c r="K4" t="n">
-        <v>35.06</v>
+        <v>61.99</v>
       </c>
       <c r="L4" t="n">
-        <v>19.65</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="5">
@@ -638,28 +638,28 @@
         <v>35450</v>
       </c>
       <c r="E5" t="n">
-        <v>69.83</v>
+        <v>60.18</v>
       </c>
       <c r="F5" t="n">
-        <v>17.79</v>
+        <v>15.77</v>
       </c>
       <c r="G5" t="n">
-        <v>-53.89</v>
+        <v>-50.14</v>
       </c>
       <c r="H5" t="n">
-        <v>0.792</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>19.16</v>
+        <v>31.44</v>
       </c>
       <c r="J5" t="n">
-        <v>44.19</v>
+        <v>17.35</v>
       </c>
       <c r="K5" t="n">
-        <v>69.47</v>
+        <v>53.93</v>
       </c>
       <c r="L5" t="n">
-        <v>-44.99</v>
+        <v>-32.62</v>
       </c>
     </row>
     <row r="6">
@@ -682,28 +682,28 @@
         <v>36911</v>
       </c>
       <c r="E6" t="n">
-        <v>-26.87</v>
+        <v>-37.37</v>
       </c>
       <c r="F6" t="n">
-        <v>18.34</v>
+        <v>15.25</v>
       </c>
       <c r="G6" t="n">
-        <v>-63.36</v>
+        <v>-65.98999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.303</v>
+        <v>-0.656</v>
       </c>
       <c r="I6" t="n">
-        <v>-30.19</v>
+        <v>-37.91</v>
       </c>
       <c r="J6" t="n">
-        <v>-34.03</v>
+        <v>-38.1</v>
       </c>
       <c r="K6" t="n">
-        <v>47.37</v>
+        <v>55.55</v>
       </c>
       <c r="L6" t="n">
-        <v>10.46</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="7">
@@ -726,28 +726,28 @@
         <v>38372</v>
       </c>
       <c r="E7" t="n">
-        <v>-27.14</v>
+        <v>-22.82</v>
       </c>
       <c r="F7" t="n">
-        <v>17.32</v>
+        <v>14.7</v>
       </c>
       <c r="G7" t="n">
-        <v>-48.18</v>
+        <v>-47.34</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.365</v>
+        <v>-0.354</v>
       </c>
       <c r="I7" t="n">
-        <v>4.57</v>
+        <v>10.48</v>
       </c>
       <c r="J7" t="n">
-        <v>4.85</v>
+        <v>5.47</v>
       </c>
       <c r="K7" t="n">
-        <v>15.57</v>
+        <v>3.6</v>
       </c>
       <c r="L7" t="n">
-        <v>-42.42</v>
+        <v>-35.47</v>
       </c>
     </row>
     <row r="8">
@@ -770,28 +770,28 @@
         <v>39833</v>
       </c>
       <c r="E8" t="n">
-        <v>130.34</v>
+        <v>130.06</v>
       </c>
       <c r="F8" t="n">
-        <v>18.68</v>
+        <v>14.83</v>
       </c>
       <c r="G8" t="n">
-        <v>-14.77</v>
+        <v>-16.84</v>
       </c>
       <c r="H8" t="n">
-        <v>1.157</v>
+        <v>1.407</v>
       </c>
       <c r="I8" t="n">
-        <v>59.71</v>
+        <v>49.55</v>
       </c>
       <c r="J8" t="n">
-        <v>19.66</v>
+        <v>25.74</v>
       </c>
       <c r="K8" t="n">
-        <v>2.83</v>
+        <v>6.75</v>
       </c>
       <c r="L8" t="n">
-        <v>15.89</v>
+        <v>14.37</v>
       </c>
     </row>
     <row r="9">
@@ -814,28 +814,28 @@
         <v>41294</v>
       </c>
       <c r="E9" t="n">
-        <v>82.88</v>
+        <v>82.31</v>
       </c>
       <c r="F9" t="n">
-        <v>18.81</v>
+        <v>14.4</v>
       </c>
       <c r="G9" t="n">
-        <v>-12.09</v>
+        <v>-11.9</v>
       </c>
       <c r="H9" t="n">
-        <v>0.88</v>
+        <v>1.082</v>
       </c>
       <c r="I9" t="n">
-        <v>36.04</v>
+        <v>27.02</v>
       </c>
       <c r="J9" t="n">
-        <v>19.58</v>
+        <v>18.3</v>
       </c>
       <c r="K9" t="n">
-        <v>8.800000000000001</v>
+        <v>5.18</v>
       </c>
       <c r="L9" t="n">
-        <v>8.220000000000001</v>
+        <v>16.19</v>
       </c>
     </row>
     <row r="10">
@@ -858,28 +858,28 @@
         <v>42755</v>
       </c>
       <c r="E10" t="n">
-        <v>163.32</v>
+        <v>154.62</v>
       </c>
       <c r="F10" t="n">
-        <v>19.12</v>
+        <v>13.8</v>
       </c>
       <c r="G10" t="n">
-        <v>-33.07</v>
+        <v>-21.61</v>
       </c>
       <c r="H10" t="n">
-        <v>1.318</v>
+        <v>1.709</v>
       </c>
       <c r="I10" t="n">
-        <v>28.54</v>
+        <v>35.28</v>
       </c>
       <c r="J10" t="n">
-        <v>2.21</v>
+        <v>-5.04</v>
       </c>
       <c r="K10" t="n">
-        <v>39.51</v>
+        <v>32</v>
       </c>
       <c r="L10" t="n">
-        <v>42.36</v>
+        <v>44.78</v>
       </c>
     </row>
     <row r="11">
@@ -902,28 +902,28 @@
         <v>44216</v>
       </c>
       <c r="E11" t="n">
-        <v>65.48999999999999</v>
+        <v>63.55</v>
       </c>
       <c r="F11" t="n">
-        <v>17.83</v>
+        <v>13.84</v>
       </c>
       <c r="G11" t="n">
-        <v>-35.24</v>
+        <v>-34.22</v>
       </c>
       <c r="H11" t="n">
-        <v>0.764</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>23.58</v>
+        <v>15.64</v>
       </c>
       <c r="J11" t="n">
-        <v>-28.43</v>
+        <v>-21.79</v>
       </c>
       <c r="K11" t="n">
-        <v>51.52</v>
+        <v>45.31</v>
       </c>
       <c r="L11" t="n">
-        <v>24.83</v>
+        <v>24.22</v>
       </c>
     </row>
     <row r="12">
@@ -946,22 +946,22 @@
         <v>45677</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-10.12</v>
       </c>
       <c r="F12" t="n">
-        <v>18.87</v>
+        <v>13.8</v>
       </c>
       <c r="G12" t="n">
-        <v>-10.9</v>
+        <v>-13.6</v>
       </c>
       <c r="H12" t="n">
-        <v>0.051</v>
+        <v>-0.576</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.82</v>
+        <v>-11.07</v>
       </c>
       <c r="J12" t="n">
-        <v>0.55</v>
+        <v>0.18</v>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1012,7 +1012,7 @@
         <v>1985</v>
       </c>
       <c r="B2" t="n">
-        <v>32.51257462380239</v>
+        <v>30.71590095049119</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>1986</v>
       </c>
       <c r="B3" t="n">
-        <v>9.177631994635306</v>
+        <v>10.42194081455774</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>1987</v>
       </c>
       <c r="B4" t="n">
-        <v>-16.72139916633481</v>
+        <v>-0.09619138288430307</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>1988</v>
       </c>
       <c r="B5" t="n">
-        <v>22.78699784650831</v>
+        <v>3.67321023460927</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>1989</v>
       </c>
       <c r="B6" t="n">
-        <v>20.14601871364299</v>
+        <v>15.58269899111788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>1990</v>
       </c>
       <c r="B7" t="n">
-        <v>-12.8815147538767</v>
+        <v>-15.78334604805196</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>1991</v>
       </c>
       <c r="B8" t="n">
-        <v>39.72382401034444</v>
+        <v>52.762521465919</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>1992</v>
       </c>
       <c r="B9" t="n">
-        <v>20.0967469508667</v>
+        <v>14.79287390255457</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>1993</v>
       </c>
       <c r="B10" t="n">
-        <v>19.13132799033657</v>
+        <v>16.86024728829318</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>1994</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.3293518802572781</v>
+        <v>-3.081210282267444</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>1995</v>
       </c>
       <c r="B12" t="n">
-        <v>37.29808142858231</v>
+        <v>62.16372091517319</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>1996</v>
       </c>
       <c r="B13" t="n">
-        <v>14.57398031971593</v>
+        <v>21.51945470044119</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>1997</v>
       </c>
       <c r="B14" t="n">
-        <v>24.57083388445385</v>
+        <v>33.54998990496649</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>1998</v>
       </c>
       <c r="B15" t="n">
-        <v>41.94356323530481</v>
+        <v>11.14383891473734</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>1999</v>
       </c>
       <c r="B16" t="n">
-        <v>68.91256842055562</v>
+        <v>68.90981798870072</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>2000</v>
       </c>
       <c r="B17" t="n">
-        <v>-38.51562458242992</v>
+        <v>-36.15696325896537</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>2001</v>
       </c>
       <c r="B18" t="n">
-        <v>-32.36844315443101</v>
+        <v>-33.42644624893246</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>2002</v>
       </c>
       <c r="B19" t="n">
-        <v>-37.51785777016418</v>
+        <v>-37.02051488906983</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>2003</v>
       </c>
       <c r="B20" t="n">
-        <v>46.2126073094379</v>
+        <v>47.8699589905118</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>2004</v>
       </c>
       <c r="B21" t="n">
-        <v>12.12367141046256</v>
+        <v>10.68013329260438</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>2005</v>
       </c>
       <c r="B22" t="n">
-        <v>3.898622086105208</v>
+        <v>3.280985811116044</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>2006</v>
       </c>
       <c r="B23" t="n">
-        <v>4.373277781018614</v>
+        <v>5.122017657188915</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>2007</v>
       </c>
       <c r="B24" t="n">
-        <v>18.07048330134535</v>
+        <v>18.86509824366005</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>2008</v>
       </c>
       <c r="B25" t="n">
-        <v>-41.58980108678499</v>
+        <v>-41.45728370768639</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>2009</v>
       </c>
       <c r="B26" t="n">
-        <v>53.0812110611975</v>
+        <v>54.94710248453325</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>2010</v>
       </c>
       <c r="B27" t="n">
-        <v>19.20950688887302</v>
+        <v>20.22697189733118</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>2011</v>
       </c>
       <c r="B28" t="n">
-        <v>5.152638317905556</v>
+        <v>1.29847055742327</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>2012</v>
       </c>
       <c r="B29" t="n">
-        <v>16.14146567360519</v>
+        <v>18.02758176333592</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>2013</v>
       </c>
       <c r="B30" t="n">
-        <v>34.06795525506987</v>
+        <v>35.69291875442899</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>2014</v>
       </c>
       <c r="B31" t="n">
-        <v>17.18539789917597</v>
+        <v>17.2509565446989</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>2015</v>
       </c>
       <c r="B32" t="n">
-        <v>10.24774272292877</v>
+        <v>9.046406139273522</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>2016</v>
       </c>
       <c r="B33" t="n">
-        <v>4.217533826675157</v>
+        <v>5.494968202251527</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>2017</v>
       </c>
       <c r="B34" t="n">
-        <v>27.32127507529745</v>
+        <v>39.03308646033123</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>2018</v>
       </c>
       <c r="B35" t="n">
-        <v>0.06639583520637871</v>
+        <v>-4.728078023799331</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>2019</v>
       </c>
       <c r="B36" t="n">
-        <v>38.64550736759074</v>
+        <v>39.65271508652133</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>2020</v>
       </c>
       <c r="B37" t="n">
-        <v>47.62275554846012</v>
+        <v>45.6942083762633</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>2021</v>
       </c>
       <c r="B38" t="n">
-        <v>26.99715139844237</v>
+        <v>26.50657706462243</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>2022</v>
       </c>
       <c r="B39" t="n">
-        <v>-32.73127877452779</v>
+        <v>-32.03852112897635</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>2023</v>
       </c>
       <c r="B40" t="n">
-        <v>53.07849248311991</v>
+        <v>52.59568250914413</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>2024</v>
       </c>
       <c r="B41" t="n">
-        <v>27.81369992635589</v>
+        <v>25.89687538809888</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>2025</v>
       </c>
       <c r="B42" t="n">
-        <v>-2.64439463590348</v>
+        <v>-12.06818912733514</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>2026</v>
       </c>
       <c r="B43" t="n">
-        <v>-0.1564263538767152</v>
+        <v>1.21488080258727</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1932,13 +1932,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.070143010701801</v>
+        <v>3.227911000911538</v>
       </c>
       <c r="C2" t="n">
-        <v>1.372853742379143</v>
+        <v>3.803600226083659</v>
       </c>
       <c r="D2" t="n">
-        <v>3.413742183634067</v>
+        <v>6.891609993982838</v>
       </c>
       <c r="E2" t="n">
         <v>41</v>
@@ -1951,13 +1951,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.04314961651837</v>
+        <v>1.055302173023664</v>
       </c>
       <c r="C3" t="n">
-        <v>1.109674570619013</v>
+        <v>0.836622700968237</v>
       </c>
       <c r="D3" t="n">
-        <v>3.141261567811253</v>
+        <v>6.803735200291657</v>
       </c>
       <c r="E3" t="n">
         <v>42</v>
@@ -1970,13 +1970,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.05078432521763303</v>
+        <v>0.9667912599904411</v>
       </c>
       <c r="C4" t="n">
-        <v>1.32895117039491</v>
+        <v>1.084636744595924</v>
       </c>
       <c r="D4" t="n">
-        <v>6.146338340377562</v>
+        <v>6.193264463067968</v>
       </c>
       <c r="E4" t="n">
         <v>42</v>
@@ -1989,13 +1989,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.638377527823313</v>
+        <v>1.310550949918292</v>
       </c>
       <c r="C5" t="n">
-        <v>1.416492094314359</v>
+        <v>1.248020175680531</v>
       </c>
       <c r="D5" t="n">
-        <v>3.592344679692699</v>
+        <v>6.755559517008316</v>
       </c>
       <c r="E5" t="n">
         <v>41</v>
@@ -2008,13 +2008,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.248252937466691</v>
+        <v>1.709414629134797</v>
       </c>
       <c r="C6" t="n">
-        <v>1.509841583665184</v>
+        <v>1.988571090605662</v>
       </c>
       <c r="D6" t="n">
-        <v>3.639762642615902</v>
+        <v>5.243900363824967</v>
       </c>
       <c r="E6" t="n">
         <v>41</v>
@@ -2027,13 +2027,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.301011618587115</v>
+        <v>1.072706630737566</v>
       </c>
       <c r="C7" t="n">
-        <v>0.843996204183517</v>
+        <v>0.5576394526316752</v>
       </c>
       <c r="D7" t="n">
-        <v>3.977983476933904</v>
+        <v>5.444803073174385</v>
       </c>
       <c r="E7" t="n">
         <v>41</v>
@@ -2046,13 +2046,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5460511569860163</v>
+        <v>2.230602765886138</v>
       </c>
       <c r="C8" t="n">
-        <v>1.922258183440495</v>
+        <v>2.085191211849424</v>
       </c>
       <c r="D8" t="n">
-        <v>4.038290581884267</v>
+        <v>5.549830610960716</v>
       </c>
       <c r="E8" t="n">
         <v>41</v>
@@ -2065,13 +2065,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.1727216152657146</v>
+        <v>0.4481747178176048</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5744948094100089</v>
+        <v>1.983210850890016</v>
       </c>
       <c r="D9" t="n">
-        <v>3.456134622823505</v>
+        <v>5.965533941887427</v>
       </c>
       <c r="E9" t="n">
         <v>41</v>
@@ -2084,13 +2084,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1697132621184768</v>
+        <v>-1.611285170377071</v>
       </c>
       <c r="C10" t="n">
-        <v>1.553098380082907</v>
+        <v>0.3052780329940719</v>
       </c>
       <c r="D10" t="n">
-        <v>4.859935093569446</v>
+        <v>6.971357339570307</v>
       </c>
       <c r="E10" t="n">
         <v>41</v>
@@ -2103,13 +2103,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.0401647597459046</v>
+        <v>0.8565971186768464</v>
       </c>
       <c r="C11" t="n">
-        <v>1.026887641024854</v>
+        <v>2.183088986542225</v>
       </c>
       <c r="D11" t="n">
-        <v>4.595129251348676</v>
+        <v>8.685360532896983</v>
       </c>
       <c r="E11" t="n">
         <v>41</v>
@@ -2122,13 +2122,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.236256867190412</v>
+        <v>2.291335543787179</v>
       </c>
       <c r="C12" t="n">
-        <v>1.734123406536603</v>
+        <v>2.608936903196901</v>
       </c>
       <c r="D12" t="n">
-        <v>4.186238182416875</v>
+        <v>6.190266473572652</v>
       </c>
       <c r="E12" t="n">
         <v>41</v>
@@ -2141,13 +2141,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.174719201143924</v>
+        <v>-0.4081138058079508</v>
       </c>
       <c r="C13" t="n">
-        <v>1.051599894253763</v>
+        <v>0.08233941872664019</v>
       </c>
       <c r="D13" t="n">
-        <v>4.630598365072607</v>
+        <v>6.098617980911362</v>
       </c>
       <c r="E13" t="n">
         <v>41</v>
@@ -2191,13 +2191,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.057730436897849</v>
+        <v>5.696851175360692</v>
       </c>
       <c r="C2" t="n">
-        <v>4.392895659000473</v>
+        <v>4.279021733705457</v>
       </c>
       <c r="D2" t="n">
-        <v>10.05028247991938</v>
+        <v>13.02324642005261</v>
       </c>
     </row>
     <row r="3">
@@ -2207,13 +2207,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.732400551481327</v>
+        <v>4.127629719876613</v>
       </c>
       <c r="C3" t="n">
-        <v>3.460351205561252</v>
+        <v>3.513522959957771</v>
       </c>
       <c r="D3" t="n">
-        <v>11.79644224676931</v>
+        <v>11.00270396661483</v>
       </c>
     </row>
     <row r="4">
@@ -2223,13 +2223,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.065096606407856</v>
+        <v>1.038102327313502</v>
       </c>
       <c r="C4" t="n">
-        <v>4.037675458946555</v>
+        <v>3.809279840339252</v>
       </c>
       <c r="D4" t="n">
-        <v>10.56844570173146</v>
+        <v>11.99811133880759</v>
       </c>
     </row>
     <row r="5">
@@ -2239,13 +2239,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.125652224167355</v>
+        <v>2.789424597019876</v>
       </c>
       <c r="C5" t="n">
-        <v>4.25609717968336</v>
+        <v>4.273332364810489</v>
       </c>
       <c r="D5" t="n">
-        <v>10.88630991548031</v>
+        <v>12.11453576429858</v>
       </c>
     </row>
   </sheetData>
@@ -2296,16 +2296,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>83.61333333333333</v>
+        <v>84.32833333333333</v>
       </c>
       <c r="C2" t="n">
-        <v>84.7</v>
+        <v>97.55500000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>-26.87</v>
+        <v>-37.37</v>
       </c>
       <c r="E2" t="n">
-        <v>163.32</v>
+        <v>154.62</v>
       </c>
       <c r="F2" t="n">
         <v>6</v>
@@ -2318,16 +2318,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35.502</v>
+        <v>34.72</v>
       </c>
       <c r="C3" t="n">
-        <v>52.88</v>
+        <v>60.18</v>
       </c>
       <c r="D3" t="n">
-        <v>-27.14</v>
+        <v>-22.82</v>
       </c>
       <c r="E3" t="n">
-        <v>82.88</v>
+        <v>82.31</v>
       </c>
       <c r="F3" t="n">
         <v>5</v>

--- a/nasdaq_presidential_analysis.xlsx
+++ b/nasdaq_presidential_analysis.xlsx
@@ -506,28 +506,28 @@
         <v>31067</v>
       </c>
       <c r="E2" t="n">
-        <v>64.05</v>
+        <v>63.88</v>
       </c>
       <c r="F2" t="n">
-        <v>14.29</v>
+        <v>12.29</v>
       </c>
       <c r="G2" t="n">
-        <v>-38.83</v>
+        <v>-38.65</v>
       </c>
       <c r="H2" t="n">
-        <v>0.915</v>
+        <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>40.27</v>
+        <v>40.21</v>
       </c>
       <c r="J2" t="n">
-        <v>12.78</v>
+        <v>13.05</v>
       </c>
       <c r="K2" t="n">
-        <v>-4.19</v>
+        <v>-4.37</v>
       </c>
       <c r="L2" t="n">
-        <v>6.76</v>
+        <v>6.66</v>
       </c>
     </row>
     <row r="3">
@@ -550,28 +550,28 @@
         <v>32528</v>
       </c>
       <c r="E3" t="n">
-        <v>70.23999999999999</v>
+        <v>70.05</v>
       </c>
       <c r="F3" t="n">
-        <v>14.14</v>
+        <v>12.01</v>
       </c>
       <c r="G3" t="n">
-        <v>-36.32</v>
+        <v>-36.28</v>
       </c>
       <c r="H3" t="n">
-        <v>0.956</v>
+        <v>1.106</v>
       </c>
       <c r="I3" t="n">
-        <v>6.81</v>
+        <v>6.58</v>
       </c>
       <c r="J3" t="n">
-        <v>-4.89</v>
+        <v>-5</v>
       </c>
       <c r="K3" t="n">
-        <v>46.35</v>
+        <v>46.56</v>
       </c>
       <c r="L3" t="n">
-        <v>15.12</v>
+        <v>15.05</v>
       </c>
     </row>
     <row r="4">
@@ -594,28 +594,28 @@
         <v>33989</v>
       </c>
       <c r="E4" t="n">
-        <v>124.87</v>
+        <v>124.91</v>
       </c>
       <c r="F4" t="n">
-        <v>13.79</v>
+        <v>11.59</v>
       </c>
       <c r="G4" t="n">
-        <v>-13.26</v>
+        <v>-13.06</v>
       </c>
       <c r="H4" t="n">
-        <v>1.49</v>
+        <v>1.75</v>
       </c>
       <c r="I4" t="n">
-        <v>14.12</v>
+        <v>14.14</v>
       </c>
       <c r="J4" t="n">
-        <v>-4.74</v>
+        <v>-4.49</v>
       </c>
       <c r="K4" t="n">
-        <v>61.99</v>
+        <v>62.01</v>
       </c>
       <c r="L4" t="n">
-        <v>25.6</v>
+        <v>25.53</v>
       </c>
     </row>
     <row r="5">
@@ -638,25 +638,25 @@
         <v>35450</v>
       </c>
       <c r="E5" t="n">
-        <v>60.18</v>
+        <v>60.31</v>
       </c>
       <c r="F5" t="n">
-        <v>15.77</v>
+        <v>13.79</v>
       </c>
       <c r="G5" t="n">
-        <v>-50.14</v>
+        <v>-50.1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="I5" t="n">
-        <v>31.44</v>
+        <v>31.47</v>
       </c>
       <c r="J5" t="n">
-        <v>17.35</v>
+        <v>17.47</v>
       </c>
       <c r="K5" t="n">
-        <v>53.93</v>
+        <v>53.56</v>
       </c>
       <c r="L5" t="n">
         <v>-32.62</v>
@@ -682,28 +682,28 @@
         <v>36911</v>
       </c>
       <c r="E6" t="n">
-        <v>-37.37</v>
+        <v>-37.39</v>
       </c>
       <c r="F6" t="n">
-        <v>15.25</v>
+        <v>13.33</v>
       </c>
       <c r="G6" t="n">
-        <v>-65.98999999999999</v>
+        <v>-65.89</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.656</v>
+        <v>-0.772</v>
       </c>
       <c r="I6" t="n">
-        <v>-37.91</v>
+        <v>-37.95</v>
       </c>
       <c r="J6" t="n">
-        <v>-38.1</v>
+        <v>-38.11</v>
       </c>
       <c r="K6" t="n">
-        <v>55.55</v>
+        <v>55.61</v>
       </c>
       <c r="L6" t="n">
-        <v>4.92</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="7">
@@ -726,28 +726,28 @@
         <v>38372</v>
       </c>
       <c r="E7" t="n">
-        <v>-22.82</v>
+        <v>-23.01</v>
       </c>
       <c r="F7" t="n">
-        <v>14.7</v>
+        <v>12.52</v>
       </c>
       <c r="G7" t="n">
-        <v>-47.34</v>
+        <v>-47.14</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.354</v>
+        <v>-0.445</v>
       </c>
       <c r="I7" t="n">
-        <v>10.48</v>
+        <v>10.33</v>
       </c>
       <c r="J7" t="n">
-        <v>5.47</v>
+        <v>5.5</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="L7" t="n">
-        <v>-35.47</v>
+        <v>-35.7</v>
       </c>
     </row>
     <row r="8">
@@ -770,28 +770,28 @@
         <v>39833</v>
       </c>
       <c r="E8" t="n">
-        <v>130.06</v>
+        <v>130.32</v>
       </c>
       <c r="F8" t="n">
-        <v>14.83</v>
+        <v>12.6</v>
       </c>
       <c r="G8" t="n">
-        <v>-16.84</v>
+        <v>-16.5</v>
       </c>
       <c r="H8" t="n">
-        <v>1.407</v>
+        <v>1.639</v>
       </c>
       <c r="I8" t="n">
-        <v>49.55</v>
+        <v>49.64</v>
       </c>
       <c r="J8" t="n">
-        <v>25.74</v>
+        <v>25.9</v>
       </c>
       <c r="K8" t="n">
-        <v>6.75</v>
+        <v>6.7</v>
       </c>
       <c r="L8" t="n">
-        <v>14.37</v>
+        <v>14.28</v>
       </c>
     </row>
     <row r="9">
@@ -814,28 +814,28 @@
         <v>41294</v>
       </c>
       <c r="E9" t="n">
-        <v>82.31</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>14.4</v>
+        <v>12.11</v>
       </c>
       <c r="G9" t="n">
-        <v>-11.9</v>
+        <v>-11.5</v>
       </c>
       <c r="H9" t="n">
-        <v>1.082</v>
+        <v>1.26</v>
       </c>
       <c r="I9" t="n">
-        <v>27.02</v>
+        <v>26.72</v>
       </c>
       <c r="J9" t="n">
-        <v>18.3</v>
+        <v>18.41</v>
       </c>
       <c r="K9" t="n">
-        <v>5.18</v>
+        <v>5.09</v>
       </c>
       <c r="L9" t="n">
-        <v>16.19</v>
+        <v>16.33</v>
       </c>
     </row>
     <row r="10">
@@ -858,28 +858,28 @@
         <v>42755</v>
       </c>
       <c r="E10" t="n">
-        <v>154.62</v>
+        <v>160.29</v>
       </c>
       <c r="F10" t="n">
-        <v>13.8</v>
+        <v>13.16</v>
       </c>
       <c r="G10" t="n">
-        <v>-21.61</v>
+        <v>-27.46</v>
       </c>
       <c r="H10" t="n">
-        <v>1.709</v>
+        <v>1.828</v>
       </c>
       <c r="I10" t="n">
-        <v>35.28</v>
+        <v>35.38</v>
       </c>
       <c r="J10" t="n">
-        <v>-5.04</v>
+        <v>-4.81</v>
       </c>
       <c r="K10" t="n">
-        <v>32</v>
+        <v>36.15</v>
       </c>
       <c r="L10" t="n">
-        <v>44.78</v>
+        <v>44.02</v>
       </c>
     </row>
     <row r="11">
@@ -902,28 +902,28 @@
         <v>44216</v>
       </c>
       <c r="E11" t="n">
-        <v>63.55</v>
+        <v>65.16</v>
       </c>
       <c r="F11" t="n">
-        <v>13.84</v>
+        <v>14.39</v>
       </c>
       <c r="G11" t="n">
-        <v>-34.22</v>
+        <v>-35.62</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.906</v>
       </c>
       <c r="I11" t="n">
-        <v>15.64</v>
+        <v>9.81</v>
       </c>
       <c r="J11" t="n">
-        <v>-21.79</v>
+        <v>-17.73</v>
       </c>
       <c r="K11" t="n">
-        <v>45.31</v>
+        <v>44.97</v>
       </c>
       <c r="L11" t="n">
-        <v>24.22</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="12">
@@ -946,22 +946,22 @@
         <v>45677</v>
       </c>
       <c r="E12" t="n">
-        <v>-10.12</v>
+        <v>7.31</v>
       </c>
       <c r="F12" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="G12" t="n">
-        <v>-13.6</v>
+        <v>-20.84</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.576</v>
+        <v>0.486</v>
       </c>
       <c r="I12" t="n">
-        <v>-11.07</v>
+        <v>17.74</v>
       </c>
       <c r="J12" t="n">
-        <v>0.18</v>
+        <v>-9.49</v>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1012,7 +1012,7 @@
         <v>1985</v>
       </c>
       <c r="B2" t="n">
-        <v>30.71590095049119</v>
+        <v>30.86756244120117</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>1986</v>
       </c>
       <c r="B3" t="n">
-        <v>10.42194081455774</v>
+        <v>10.66976824401504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1054,7 +1054,7 @@
         <v>1987</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.09619138288430307</v>
+        <v>0.05367169180008347</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>1988</v>
       </c>
       <c r="B5" t="n">
-        <v>3.67321023460927</v>
+        <v>3.74554171044128</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>1989</v>
       </c>
       <c r="B6" t="n">
-        <v>15.58269899111788</v>
+        <v>15.59752226084634</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>1990</v>
       </c>
       <c r="B7" t="n">
-        <v>-15.78334604805196</v>
+        <v>-15.86254458051123</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>1991</v>
       </c>
       <c r="B8" t="n">
-        <v>52.762521465919</v>
+        <v>52.9257856772837</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>1992</v>
       </c>
       <c r="B9" t="n">
-        <v>14.79287390255457</v>
+        <v>14.65101232259225</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
         <v>1993</v>
       </c>
       <c r="B10" t="n">
-        <v>16.86024728829318</v>
+        <v>16.69982882937944</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>1994</v>
       </c>
       <c r="B11" t="n">
-        <v>-3.081210282267444</v>
+        <v>-2.989970269633435</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>1995</v>
       </c>
       <c r="B12" t="n">
-        <v>62.16372091517319</v>
+        <v>62.2265833349031</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>1996</v>
       </c>
       <c r="B13" t="n">
-        <v>21.51945470044119</v>
+        <v>21.36271978184512</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>1997</v>
       </c>
       <c r="B14" t="n">
-        <v>33.54998990496649</v>
+        <v>33.28046233463813</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>1998</v>
       </c>
       <c r="B15" t="n">
-        <v>11.14383891473734</v>
+        <v>11.0691789620158</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>1999</v>
       </c>
       <c r="B16" t="n">
-        <v>68.90981798870072</v>
+        <v>68.70434316196905</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>2000</v>
       </c>
       <c r="B17" t="n">
-        <v>-36.15696325896537</v>
+        <v>-36.27969852200538</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>2001</v>
       </c>
       <c r="B18" t="n">
-        <v>-33.42644624893246</v>
+        <v>-33.34979539852193</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>2002</v>
       </c>
       <c r="B19" t="n">
-        <v>-37.02051488906983</v>
+        <v>-37.11312707399335</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         <v>2003</v>
       </c>
       <c r="B20" t="n">
-        <v>47.8699589905118</v>
+        <v>48.05935467789537</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>2004</v>
       </c>
       <c r="B21" t="n">
-        <v>10.68013329260438</v>
+        <v>10.62681235369767</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>2005</v>
       </c>
       <c r="B22" t="n">
-        <v>3.280985811116044</v>
+        <v>3.311284113865876</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>2006</v>
       </c>
       <c r="B23" t="n">
-        <v>5.122017657188915</v>
+        <v>5.045588095486764</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>2007</v>
       </c>
       <c r="B24" t="n">
-        <v>18.86509824366005</v>
+        <v>18.76017540102857</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>2008</v>
       </c>
       <c r="B25" t="n">
-        <v>-41.45728370768639</v>
+        <v>-41.46431934687953</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>2009</v>
       </c>
       <c r="B26" t="n">
-        <v>54.94710248453325</v>
+        <v>54.72478493000308</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1537,7 +1537,7 @@
         <v>2010</v>
       </c>
       <c r="B27" t="n">
-        <v>20.22697189733118</v>
+        <v>20.10409228270249</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>2011</v>
       </c>
       <c r="B28" t="n">
-        <v>1.29847055742327</v>
+        <v>1.494865509068788</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>2012</v>
       </c>
       <c r="B29" t="n">
-        <v>18.02758176333592</v>
+        <v>17.73236847727451</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>2013</v>
       </c>
       <c r="B30" t="n">
-        <v>35.69291875442899</v>
+        <v>35.50601517909189</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>2014</v>
       </c>
       <c r="B31" t="n">
-        <v>17.2509565446989</v>
+        <v>17.39323876809415</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>2015</v>
       </c>
       <c r="B32" t="n">
-        <v>9.046406139273522</v>
+        <v>8.975848454005874</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>2016</v>
       </c>
       <c r="B33" t="n">
-        <v>5.494968202251527</v>
+        <v>5.634019598307449</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>2017</v>
       </c>
       <c r="B34" t="n">
-        <v>39.03308646033123</v>
+        <v>38.74296768847012</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>2018</v>
       </c>
       <c r="B35" t="n">
-        <v>-4.728078023799331</v>
+        <v>-4.945842728519223</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         <v>2019</v>
       </c>
       <c r="B36" t="n">
-        <v>39.65271508652133</v>
+        <v>39.37084550654721</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>2020</v>
       </c>
       <c r="B37" t="n">
-        <v>45.6942083762633</v>
+        <v>46.66181898946586</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>2021</v>
       </c>
       <c r="B38" t="n">
-        <v>26.50657706462243</v>
+        <v>20.44069933096764</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>2022</v>
       </c>
       <c r="B39" t="n">
-        <v>-32.03852112897635</v>
+        <v>-28.89293165087062</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>2023</v>
       </c>
       <c r="B40" t="n">
-        <v>52.59568250914413</v>
+        <v>48.25866004069388</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>2024</v>
       </c>
       <c r="B41" t="n">
-        <v>25.89687538809888</v>
+        <v>30.14891021515105</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>2025</v>
       </c>
       <c r="B42" t="n">
-        <v>-12.06818912733514</v>
+        <v>19.43387074815934</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>2026</v>
       </c>
       <c r="B43" t="n">
-        <v>1.21488080258727</v>
+        <v>-8.511495102897193</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1932,13 +1932,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.227911000911538</v>
+        <v>3.724261614079884</v>
       </c>
       <c r="C2" t="n">
-        <v>3.803600226083659</v>
+        <v>4.759927219271876</v>
       </c>
       <c r="D2" t="n">
-        <v>6.891609993982838</v>
+        <v>6.71780510529517</v>
       </c>
       <c r="E2" t="n">
         <v>41</v>
@@ -1951,13 +1951,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.055302173023664</v>
+        <v>0.5798256375881964</v>
       </c>
       <c r="C3" t="n">
-        <v>0.836622700968237</v>
+        <v>0.529489868458155</v>
       </c>
       <c r="D3" t="n">
-        <v>6.803735200291657</v>
+        <v>6.857596845911385</v>
       </c>
       <c r="E3" t="n">
         <v>42</v>
@@ -1970,13 +1970,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9667912599904411</v>
+        <v>0.8109183504585028</v>
       </c>
       <c r="C4" t="n">
-        <v>1.084636744595924</v>
+        <v>0.9863926131880918</v>
       </c>
       <c r="D4" t="n">
-        <v>6.193264463067968</v>
+        <v>6.593179826929935</v>
       </c>
       <c r="E4" t="n">
         <v>42</v>
@@ -1989,13 +1989,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.310550949918292</v>
+        <v>1.589603334033249</v>
       </c>
       <c r="C5" t="n">
-        <v>1.248020175680531</v>
+        <v>1.933409208796188</v>
       </c>
       <c r="D5" t="n">
-        <v>6.755559517008316</v>
+        <v>6.599245091095855</v>
       </c>
       <c r="E5" t="n">
         <v>41</v>
@@ -2008,13 +2008,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.709414629134797</v>
+        <v>1.89508245840882</v>
       </c>
       <c r="C6" t="n">
-        <v>1.988571090605662</v>
+        <v>2.573786067974826</v>
       </c>
       <c r="D6" t="n">
-        <v>5.243900363824967</v>
+        <v>5.240293000191209</v>
       </c>
       <c r="E6" t="n">
         <v>41</v>
@@ -2027,13 +2027,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.072706630737566</v>
+        <v>1.24489379779218</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5576394526316752</v>
+        <v>0.3085689818964843</v>
       </c>
       <c r="D7" t="n">
-        <v>5.444803073174385</v>
+        <v>5.292862244438011</v>
       </c>
       <c r="E7" t="n">
         <v>41</v>
@@ -2046,13 +2046,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.230602765886138</v>
+        <v>2.01636032417121</v>
       </c>
       <c r="C8" t="n">
-        <v>2.085191211849424</v>
+        <v>2.539494142149046</v>
       </c>
       <c r="D8" t="n">
-        <v>5.549830610960716</v>
+        <v>5.741582672698164</v>
       </c>
       <c r="E8" t="n">
         <v>41</v>
@@ -2065,13 +2065,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4481747178176048</v>
+        <v>0.224847260828666</v>
       </c>
       <c r="C9" t="n">
-        <v>1.983210850890016</v>
+        <v>1.594732280042166</v>
       </c>
       <c r="D9" t="n">
-        <v>5.965533941887427</v>
+        <v>5.847537609271312</v>
       </c>
       <c r="E9" t="n">
         <v>41</v>
@@ -2084,13 +2084,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-1.611285170377071</v>
+        <v>-1.179580609404011</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3052780329940719</v>
+        <v>0.09022397657039161</v>
       </c>
       <c r="D10" t="n">
-        <v>6.971357339570307</v>
+        <v>7.132853110585705</v>
       </c>
       <c r="E10" t="n">
         <v>41</v>
@@ -2103,13 +2103,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8565971186768464</v>
+        <v>1.113198067068061</v>
       </c>
       <c r="C11" t="n">
-        <v>2.183088986542225</v>
+        <v>2.162751985686051</v>
       </c>
       <c r="D11" t="n">
-        <v>8.685360532896983</v>
+        <v>8.759221407145693</v>
       </c>
       <c r="E11" t="n">
         <v>41</v>
@@ -2122,13 +2122,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.291335543787179</v>
+        <v>1.90609045307631</v>
       </c>
       <c r="C12" t="n">
-        <v>2.608936903196901</v>
+        <v>2.607260577698112</v>
       </c>
       <c r="D12" t="n">
-        <v>6.190266473572652</v>
+        <v>6.061572187888856</v>
       </c>
       <c r="E12" t="n">
         <v>41</v>
@@ -2141,13 +2141,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.4081138058079508</v>
+        <v>-0.5112274547526935</v>
       </c>
       <c r="C13" t="n">
-        <v>0.08233941872664019</v>
+        <v>0.08297593136947778</v>
       </c>
       <c r="D13" t="n">
-        <v>6.098617980911362</v>
+        <v>6.04363460717208</v>
       </c>
       <c r="E13" t="n">
         <v>41</v>
@@ -2191,13 +2191,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.696851175360692</v>
+        <v>5.460132790483087</v>
       </c>
       <c r="C2" t="n">
-        <v>4.279021733705457</v>
+        <v>4.501303845773386</v>
       </c>
       <c r="D2" t="n">
-        <v>13.02324642005261</v>
+        <v>13.18036491245608</v>
       </c>
     </row>
     <row r="3">
@@ -2207,13 +2207,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.127629719876613</v>
+        <v>4.828976807317149</v>
       </c>
       <c r="C3" t="n">
-        <v>3.513522959957771</v>
+        <v>5.234519170137153</v>
       </c>
       <c r="D3" t="n">
-        <v>11.00270396661483</v>
+        <v>11.0699535734218</v>
       </c>
     </row>
     <row r="4">
@@ -2223,13 +2223,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.038102327313502</v>
+        <v>1.059036498654893</v>
       </c>
       <c r="C4" t="n">
-        <v>3.809279840339252</v>
+        <v>3.9910037141484</v>
       </c>
       <c r="D4" t="n">
-        <v>11.99811133880759</v>
+        <v>12.03809506058722</v>
       </c>
     </row>
     <row r="5">
@@ -2239,13 +2239,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.789424597019876</v>
+        <v>2.650410341565847</v>
       </c>
       <c r="C5" t="n">
-        <v>4.273332364810489</v>
+        <v>4.531392879882379</v>
       </c>
       <c r="D5" t="n">
-        <v>12.11453576429858</v>
+        <v>11.91460874541891</v>
       </c>
     </row>
   </sheetData>
@@ -2296,16 +2296,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>84.32833333333333</v>
+        <v>85.55666666666666</v>
       </c>
       <c r="C2" t="n">
-        <v>97.55500000000001</v>
+        <v>97.47999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>-37.37</v>
+        <v>-37.39</v>
       </c>
       <c r="E2" t="n">
-        <v>154.62</v>
+        <v>160.29</v>
       </c>
       <c r="F2" t="n">
         <v>6</v>
@@ -2318,16 +2318,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.72</v>
+        <v>38.118</v>
       </c>
       <c r="C3" t="n">
-        <v>60.18</v>
+        <v>60.31</v>
       </c>
       <c r="D3" t="n">
-        <v>-22.82</v>
+        <v>-23.01</v>
       </c>
       <c r="E3" t="n">
-        <v>82.31</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="F3" t="n">
         <v>5</v>
